--- a/cmdList.xlsx
+++ b/cmdList.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Biamine\ressourcepack\Ressourcepack-for-biamine\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bianca\Desktop\Server biamine\custom plugin\1_Resourcepacks\Github\Ressourcepack-for-biamine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{916AC698-3B48-4D58-BD31-4E614FB12294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{383E4E95-2DEC-4209-A9CB-BA4237F59849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16020" yWindow="1215" windowWidth="13470" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Custom Models" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="164">
   <si>
     <t>Key (Legende)</t>
   </si>
@@ -506,13 +506,19 @@
   </si>
   <si>
     <t>pommes</t>
+  </si>
+  <si>
+    <t>cotton candy</t>
+  </si>
+  <si>
+    <t>timbits</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -579,6 +585,12 @@
       <u/>
       <sz val="18"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -662,7 +674,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -739,6 +751,15 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1047,7 +1068,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:J148"/>
+  <dimension ref="B2:J151"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -2013,68 +2034,60 @@
         <v>50</v>
       </c>
     </row>
-    <row r="75" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B75" s="23" t="s">
+    <row r="73" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B73" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C73" s="12">
+        <v>6</v>
+      </c>
+      <c r="D73" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E73" s="14" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="74" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B74" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C74" s="12">
+        <v>6</v>
+      </c>
+      <c r="D74" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="E74" s="14" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="75" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B75" s="28"/>
+      <c r="C75" s="28"/>
+      <c r="D75" s="29"/>
+      <c r="E75" s="30"/>
+    </row>
+    <row r="78" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B78" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="C75" s="24"/>
-      <c r="D75" s="24"/>
-      <c r="E75" s="24"/>
-    </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B76" s="1" t="s">
+      <c r="C78" s="24"/>
+      <c r="D78" s="24"/>
+      <c r="E78" s="24"/>
+    </row>
+    <row r="79" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B79" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="D79" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E76" s="2" t="s">
+      <c r="E79" s="2" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B77" s="12">
-        <v>1</v>
-      </c>
-      <c r="C77" s="12">
-        <v>1</v>
-      </c>
-      <c r="D77" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E77" s="14" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B78" s="12">
-        <v>1</v>
-      </c>
-      <c r="C78" s="12">
-        <v>1</v>
-      </c>
-      <c r="D78" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E78" s="14" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="79" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B79" s="12">
-        <v>1</v>
-      </c>
-      <c r="C79" s="12">
-        <v>1</v>
-      </c>
-      <c r="D79" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E79" s="14" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="80" spans="2:5" x14ac:dyDescent="0.25">
@@ -2085,146 +2098,146 @@
         <v>1</v>
       </c>
       <c r="D80" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E80" s="14" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="81" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B81" s="12">
+        <v>1</v>
+      </c>
+      <c r="C81" s="12">
+        <v>1</v>
+      </c>
+      <c r="D81" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E81" s="14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="82" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B82" s="12">
+        <v>1</v>
+      </c>
+      <c r="C82" s="12">
+        <v>1</v>
+      </c>
+      <c r="D82" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E82" s="14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="83" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B83" s="12">
+        <v>1</v>
+      </c>
+      <c r="C83" s="12">
+        <v>1</v>
+      </c>
+      <c r="D83" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E80" s="14" t="s">
+      <c r="E83" s="14" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="84" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B84" s="5"/>
-      <c r="C84" s="7" t="s">
+    <row r="87" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B87" s="5"/>
+      <c r="C87" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D84" s="5"/>
-      <c r="E84" s="6"/>
-    </row>
-    <row r="86" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B86" s="25" t="s">
+      <c r="D87" s="5"/>
+      <c r="E87" s="6"/>
+    </row>
+    <row r="89" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B89" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="C86" s="24"/>
-      <c r="D86" s="24"/>
-      <c r="E86" s="24"/>
-    </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B87" s="1" t="s">
+      <c r="C89" s="24"/>
+      <c r="D89" s="24"/>
+      <c r="E89" s="24"/>
+    </row>
+    <row r="90" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B90" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D87" s="9" t="s">
+      <c r="D90" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E87" s="2" t="s">
+      <c r="E90" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B88" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C88" s="12">
-        <v>6</v>
-      </c>
-      <c r="D88" s="15" t="s">
+    <row r="91" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B91" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C91" s="12">
+        <v>6</v>
+      </c>
+      <c r="D91" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="E88" s="16" t="s">
+      <c r="E91" s="16" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B89" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C89" s="17">
-        <v>6</v>
-      </c>
-      <c r="D89" s="18" t="s">
+    <row r="92" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B92" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C92" s="17">
+        <v>6</v>
+      </c>
+      <c r="D92" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="E89" s="19" t="s">
+      <c r="E92" s="19" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="91" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B91" s="25" t="s">
+    <row r="94" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B94" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="C91" s="24"/>
-      <c r="D91" s="24"/>
-      <c r="E91" s="24"/>
-    </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B92" s="1" t="s">
+      <c r="C94" s="24"/>
+      <c r="D94" s="24"/>
+      <c r="E94" s="24"/>
+    </row>
+    <row r="95" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B95" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D92" s="9" t="s">
+      <c r="D95" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E92" s="2" t="s">
+      <c r="E95" s="2" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B93" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C93" s="12">
-        <v>6</v>
-      </c>
-      <c r="D93" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="E93" s="16" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B94" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C94" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D94" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="E94" s="21" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B95" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C95" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D95" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="E95" s="21" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="96" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B96" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C96" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D96" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="E96" s="21" t="s">
-        <v>104</v>
+      <c r="C96" s="12">
+        <v>6</v>
+      </c>
+      <c r="D96" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="E96" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.25">
@@ -2234,8 +2247,8 @@
       <c r="C97" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D97" s="15" t="s">
-        <v>108</v>
+      <c r="D97" s="18" t="s">
+        <v>105</v>
       </c>
       <c r="E97" s="21" t="s">
         <v>104</v>
@@ -2248,8 +2261,8 @@
       <c r="C98" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D98" s="18" t="s">
-        <v>105</v>
+      <c r="D98" s="15" t="s">
+        <v>106</v>
       </c>
       <c r="E98" s="21" t="s">
         <v>104</v>
@@ -2262,8 +2275,8 @@
       <c r="C99" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D99" s="15" t="s">
-        <v>109</v>
+      <c r="D99" s="22" t="s">
+        <v>107</v>
       </c>
       <c r="E99" s="21" t="s">
         <v>104</v>
@@ -2276,8 +2289,8 @@
       <c r="C100" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D100" s="18" t="s">
-        <v>110</v>
+      <c r="D100" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E100" s="21" t="s">
         <v>104</v>
@@ -2290,8 +2303,8 @@
       <c r="C101" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D101" s="15" t="s">
-        <v>111</v>
+      <c r="D101" s="18" t="s">
+        <v>105</v>
       </c>
       <c r="E101" s="21" t="s">
         <v>104</v>
@@ -2304,8 +2317,8 @@
       <c r="C102" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D102" s="22" t="s">
-        <v>112</v>
+      <c r="D102" s="15" t="s">
+        <v>109</v>
       </c>
       <c r="E102" s="21" t="s">
         <v>104</v>
@@ -2318,8 +2331,8 @@
       <c r="C103" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D103" s="15" t="s">
-        <v>113</v>
+      <c r="D103" s="18" t="s">
+        <v>110</v>
       </c>
       <c r="E103" s="21" t="s">
         <v>104</v>
@@ -2332,8 +2345,8 @@
       <c r="C104" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D104" s="22" t="s">
-        <v>114</v>
+      <c r="D104" s="15" t="s">
+        <v>111</v>
       </c>
       <c r="E104" s="21" t="s">
         <v>104</v>
@@ -2346,8 +2359,8 @@
       <c r="C105" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D105" s="15" t="s">
-        <v>115</v>
+      <c r="D105" s="22" t="s">
+        <v>112</v>
       </c>
       <c r="E105" s="21" t="s">
         <v>104</v>
@@ -2360,8 +2373,8 @@
       <c r="C106" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D106" s="18" t="s">
-        <v>116</v>
+      <c r="D106" s="15" t="s">
+        <v>113</v>
       </c>
       <c r="E106" s="21" t="s">
         <v>104</v>
@@ -2374,8 +2387,8 @@
       <c r="C107" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D107" s="15" t="s">
-        <v>117</v>
+      <c r="D107" s="22" t="s">
+        <v>114</v>
       </c>
       <c r="E107" s="21" t="s">
         <v>104</v>
@@ -2388,8 +2401,8 @@
       <c r="C108" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D108" s="18" t="s">
-        <v>118</v>
+      <c r="D108" s="15" t="s">
+        <v>115</v>
       </c>
       <c r="E108" s="21" t="s">
         <v>104</v>
@@ -2402,8 +2415,8 @@
       <c r="C109" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D109" s="15" t="s">
-        <v>119</v>
+      <c r="D109" s="18" t="s">
+        <v>116</v>
       </c>
       <c r="E109" s="21" t="s">
         <v>104</v>
@@ -2416,8 +2429,8 @@
       <c r="C110" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D110" s="18" t="s">
-        <v>120</v>
+      <c r="D110" s="15" t="s">
+        <v>117</v>
       </c>
       <c r="E110" s="21" t="s">
         <v>104</v>
@@ -2430,8 +2443,8 @@
       <c r="C111" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D111" s="15" t="s">
-        <v>121</v>
+      <c r="D111" s="18" t="s">
+        <v>118</v>
       </c>
       <c r="E111" s="21" t="s">
         <v>104</v>
@@ -2444,8 +2457,8 @@
       <c r="C112" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D112" s="18" t="s">
-        <v>122</v>
+      <c r="D112" s="15" t="s">
+        <v>119</v>
       </c>
       <c r="E112" s="21" t="s">
         <v>104</v>
@@ -2458,8 +2471,8 @@
       <c r="C113" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D113" s="15" t="s">
-        <v>123</v>
+      <c r="D113" s="18" t="s">
+        <v>120</v>
       </c>
       <c r="E113" s="21" t="s">
         <v>104</v>
@@ -2472,8 +2485,8 @@
       <c r="C114" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D114" s="18" t="s">
-        <v>124</v>
+      <c r="D114" s="15" t="s">
+        <v>121</v>
       </c>
       <c r="E114" s="21" t="s">
         <v>104</v>
@@ -2486,8 +2499,8 @@
       <c r="C115" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D115" s="15" t="s">
-        <v>125</v>
+      <c r="D115" s="18" t="s">
+        <v>122</v>
       </c>
       <c r="E115" s="21" t="s">
         <v>104</v>
@@ -2500,8 +2513,8 @@
       <c r="C116" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D116" s="18" t="s">
-        <v>126</v>
+      <c r="D116" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="E116" s="21" t="s">
         <v>104</v>
@@ -2514,8 +2527,8 @@
       <c r="C117" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D117" s="15" t="s">
-        <v>127</v>
+      <c r="D117" s="18" t="s">
+        <v>124</v>
       </c>
       <c r="E117" s="21" t="s">
         <v>104</v>
@@ -2528,75 +2541,75 @@
       <c r="C118" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D118" s="18" t="s">
-        <v>128</v>
+      <c r="D118" s="15" t="s">
+        <v>125</v>
       </c>
       <c r="E118" s="21" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="120" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B120" s="25" t="s">
+    <row r="119" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B119" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C119" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="D119" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="E119" s="21" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="120" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B120" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C120" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="D120" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="E120" s="21" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="121" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B121" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C121" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="D121" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="E121" s="21" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="123" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B123" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="C120" s="24"/>
-      <c r="D120" s="24"/>
-      <c r="E120" s="24"/>
-    </row>
-    <row r="121" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B121" s="1" t="s">
+      <c r="C123" s="24"/>
+      <c r="D123" s="24"/>
+      <c r="E123" s="24"/>
+    </row>
+    <row r="124" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B124" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D121" s="9" t="s">
+      <c r="D124" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E121" s="2" t="s">
+      <c r="E124" s="2" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="122" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B122" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C122" s="12">
-        <v>2</v>
-      </c>
-      <c r="D122" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="E122" s="16" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="123" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B123" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C123" s="12">
-        <v>2</v>
-      </c>
-      <c r="D123" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="E123" s="16" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="124" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B124" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C124" s="12">
-        <v>2</v>
-      </c>
-      <c r="D124" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="E124" s="16" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="125" spans="2:5" x14ac:dyDescent="0.25">
@@ -2606,8 +2619,8 @@
       <c r="C125" s="12">
         <v>2</v>
       </c>
-      <c r="D125" s="22" t="s">
-        <v>134</v>
+      <c r="D125" s="15" t="s">
+        <v>131</v>
       </c>
       <c r="E125" s="16" t="s">
         <v>130</v>
@@ -2620,8 +2633,8 @@
       <c r="C126" s="12">
         <v>2</v>
       </c>
-      <c r="D126" s="15" t="s">
-        <v>135</v>
+      <c r="D126" s="18" t="s">
+        <v>132</v>
       </c>
       <c r="E126" s="16" t="s">
         <v>130</v>
@@ -2634,8 +2647,8 @@
       <c r="C127" s="12">
         <v>2</v>
       </c>
-      <c r="D127" s="18" t="s">
-        <v>136</v>
+      <c r="D127" s="15" t="s">
+        <v>133</v>
       </c>
       <c r="E127" s="16" t="s">
         <v>130</v>
@@ -2648,8 +2661,8 @@
       <c r="C128" s="12">
         <v>2</v>
       </c>
-      <c r="D128" s="15" t="s">
-        <v>137</v>
+      <c r="D128" s="22" t="s">
+        <v>134</v>
       </c>
       <c r="E128" s="16" t="s">
         <v>130</v>
@@ -2662,8 +2675,8 @@
       <c r="C129" s="12">
         <v>2</v>
       </c>
-      <c r="D129" s="22" t="s">
-        <v>138</v>
+      <c r="D129" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="E129" s="16" t="s">
         <v>130</v>
@@ -2676,8 +2689,8 @@
       <c r="C130" s="12">
         <v>2</v>
       </c>
-      <c r="D130" s="15" t="s">
-        <v>139</v>
+      <c r="D130" s="18" t="s">
+        <v>136</v>
       </c>
       <c r="E130" s="16" t="s">
         <v>130</v>
@@ -2690,8 +2703,8 @@
       <c r="C131" s="12">
         <v>2</v>
       </c>
-      <c r="D131" s="22" t="s">
-        <v>140</v>
+      <c r="D131" s="15" t="s">
+        <v>137</v>
       </c>
       <c r="E131" s="16" t="s">
         <v>130</v>
@@ -2704,8 +2717,8 @@
       <c r="C132" s="12">
         <v>2</v>
       </c>
-      <c r="D132" s="15" t="s">
-        <v>141</v>
+      <c r="D132" s="22" t="s">
+        <v>138</v>
       </c>
       <c r="E132" s="16" t="s">
         <v>130</v>
@@ -2718,8 +2731,8 @@
       <c r="C133" s="12">
         <v>2</v>
       </c>
-      <c r="D133" s="22" t="s">
-        <v>142</v>
+      <c r="D133" s="15" t="s">
+        <v>139</v>
       </c>
       <c r="E133" s="16" t="s">
         <v>130</v>
@@ -2732,8 +2745,8 @@
       <c r="C134" s="12">
         <v>2</v>
       </c>
-      <c r="D134" s="15" t="s">
-        <v>143</v>
+      <c r="D134" s="22" t="s">
+        <v>140</v>
       </c>
       <c r="E134" s="16" t="s">
         <v>130</v>
@@ -2746,8 +2759,8 @@
       <c r="C135" s="12">
         <v>2</v>
       </c>
-      <c r="D135" s="18" t="s">
-        <v>144</v>
+      <c r="D135" s="15" t="s">
+        <v>141</v>
       </c>
       <c r="E135" s="16" t="s">
         <v>130</v>
@@ -2760,8 +2773,8 @@
       <c r="C136" s="12">
         <v>2</v>
       </c>
-      <c r="D136" s="15" t="s">
-        <v>145</v>
+      <c r="D136" s="22" t="s">
+        <v>142</v>
       </c>
       <c r="E136" s="16" t="s">
         <v>130</v>
@@ -2774,8 +2787,8 @@
       <c r="C137" s="12">
         <v>2</v>
       </c>
-      <c r="D137" s="18" t="s">
-        <v>146</v>
+      <c r="D137" s="15" t="s">
+        <v>143</v>
       </c>
       <c r="E137" s="16" t="s">
         <v>130</v>
@@ -2788,8 +2801,8 @@
       <c r="C138" s="12">
         <v>2</v>
       </c>
-      <c r="D138" s="15" t="s">
-        <v>147</v>
+      <c r="D138" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="E138" s="16" t="s">
         <v>130</v>
@@ -2802,8 +2815,8 @@
       <c r="C139" s="12">
         <v>2</v>
       </c>
-      <c r="D139" s="18" t="s">
-        <v>148</v>
+      <c r="D139" s="15" t="s">
+        <v>145</v>
       </c>
       <c r="E139" s="16" t="s">
         <v>130</v>
@@ -2816,8 +2829,8 @@
       <c r="C140" s="12">
         <v>2</v>
       </c>
-      <c r="D140" s="15" t="s">
-        <v>149</v>
+      <c r="D140" s="18" t="s">
+        <v>146</v>
       </c>
       <c r="E140" s="16" t="s">
         <v>130</v>
@@ -2828,10 +2841,10 @@
         <v>5</v>
       </c>
       <c r="C141" s="12">
-        <v>6</v>
-      </c>
-      <c r="D141" s="22" t="s">
-        <v>150</v>
+        <v>2</v>
+      </c>
+      <c r="D141" s="15" t="s">
+        <v>147</v>
       </c>
       <c r="E141" s="16" t="s">
         <v>130</v>
@@ -2844,8 +2857,8 @@
       <c r="C142" s="12">
         <v>2</v>
       </c>
-      <c r="D142" s="15" t="s">
-        <v>151</v>
+      <c r="D142" s="18" t="s">
+        <v>148</v>
       </c>
       <c r="E142" s="16" t="s">
         <v>130</v>
@@ -2858,8 +2871,8 @@
       <c r="C143" s="12">
         <v>2</v>
       </c>
-      <c r="D143" s="18" t="s">
-        <v>152</v>
+      <c r="D143" s="15" t="s">
+        <v>149</v>
       </c>
       <c r="E143" s="16" t="s">
         <v>130</v>
@@ -2872,8 +2885,8 @@
       <c r="C144" s="12">
         <v>6</v>
       </c>
-      <c r="D144" s="15" t="s">
-        <v>153</v>
+      <c r="D144" s="22" t="s">
+        <v>150</v>
       </c>
       <c r="E144" s="16" t="s">
         <v>130</v>
@@ -2884,10 +2897,10 @@
         <v>5</v>
       </c>
       <c r="C145" s="12">
-        <v>6</v>
-      </c>
-      <c r="D145" s="18" t="s">
-        <v>154</v>
+        <v>2</v>
+      </c>
+      <c r="D145" s="15" t="s">
+        <v>151</v>
       </c>
       <c r="E145" s="16" t="s">
         <v>130</v>
@@ -2898,10 +2911,10 @@
         <v>5</v>
       </c>
       <c r="C146" s="12">
-        <v>6</v>
-      </c>
-      <c r="D146" s="15" t="s">
-        <v>155</v>
+        <v>2</v>
+      </c>
+      <c r="D146" s="18" t="s">
+        <v>152</v>
       </c>
       <c r="E146" s="16" t="s">
         <v>130</v>
@@ -2914,8 +2927,8 @@
       <c r="C147" s="12">
         <v>6</v>
       </c>
-      <c r="D147" s="22" t="s">
-        <v>156</v>
+      <c r="D147" s="15" t="s">
+        <v>153</v>
       </c>
       <c r="E147" s="16" t="s">
         <v>130</v>
@@ -2926,30 +2939,73 @@
         <v>5</v>
       </c>
       <c r="C148" s="12">
-        <v>2</v>
-      </c>
-      <c r="D148" s="15" t="s">
-        <v>157</v>
+        <v>6</v>
+      </c>
+      <c r="D148" s="18" t="s">
+        <v>154</v>
       </c>
       <c r="E148" s="16" t="s">
         <v>130</v>
       </c>
     </row>
+    <row r="149" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B149" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C149" s="12">
+        <v>6</v>
+      </c>
+      <c r="D149" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="E149" s="16" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="150" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B150" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C150" s="12">
+        <v>6</v>
+      </c>
+      <c r="D150" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="E150" s="16" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="151" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B151" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C151" s="12">
+        <v>2</v>
+      </c>
+      <c r="D151" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="E151" s="16" t="s">
+        <v>130</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B63:E72">
-    <sortCondition ref="D63:D72"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B63:E73">
+    <sortCondition ref="D63:D73"/>
   </sortState>
   <mergeCells count="9">
-    <mergeCell ref="B75:E75"/>
-    <mergeCell ref="B86:E86"/>
-    <mergeCell ref="B91:E91"/>
-    <mergeCell ref="B120:E120"/>
+    <mergeCell ref="B78:E78"/>
+    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="B94:E94"/>
+    <mergeCell ref="B123:E123"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B34:E34"/>
     <mergeCell ref="B15:E15"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B61:E61"/>
   </mergeCells>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/cmdList.xlsx
+++ b/cmdList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Biamine\ressourcepack\Ressourcepack-for-biamine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{916AC698-3B48-4D58-BD31-4E614FB12294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E691E5C-9CAE-4A6B-8FFA-BFB3FB363838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="163">
   <si>
     <t>Key (Legende)</t>
   </si>
@@ -506,6 +506,9 @@
   </si>
   <si>
     <t>pommes</t>
+  </si>
+  <si>
+    <t>trophy: Server B-Day</t>
   </si>
 </sst>
 </file>
@@ -1047,7 +1050,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:J148"/>
+  <dimension ref="B2:J149"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -1264,13 +1267,13 @@
         <v>5</v>
       </c>
       <c r="C20" s="12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>30</v>
+        <v>162</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
@@ -1285,10 +1288,10 @@
         <v>7</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
@@ -1303,10 +1306,10 @@
         <v>7</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
@@ -1318,13 +1321,13 @@
         <v>5</v>
       </c>
       <c r="C23" s="12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
@@ -1339,10 +1342,10 @@
         <v>8</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
@@ -1357,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
@@ -1375,10 +1378,10 @@
         <v>8</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
@@ -1393,10 +1396,10 @@
         <v>8</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
@@ -1411,10 +1414,10 @@
         <v>8</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
@@ -1429,10 +1432,10 @@
         <v>8</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
@@ -1444,13 +1447,13 @@
         <v>5</v>
       </c>
       <c r="C30" s="12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
@@ -1462,13 +1465,13 @@
         <v>5</v>
       </c>
       <c r="C31" s="12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
@@ -1483,218 +1486,222 @@
         <v>8</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="8"/>
       <c r="J32" s="4"/>
     </row>
-    <row r="34" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B34" s="23" t="s">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B33" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="12">
+        <v>8</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="4"/>
+    </row>
+    <row r="35" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B35" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24"/>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B35" s="1" t="s">
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B36" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D36" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E36" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B36" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C36" s="12">
-        <v>6</v>
-      </c>
-      <c r="D36" s="13" t="s">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B37" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="12">
+        <v>6</v>
+      </c>
+      <c r="D37" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E36" s="14" t="s">
+      <c r="E37" s="14" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B37" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C37" s="12">
-        <v>6</v>
-      </c>
-      <c r="D37" s="13" t="s">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B38" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="12">
+        <v>6</v>
+      </c>
+      <c r="D38" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="E37" s="14" t="s">
+      <c r="E38" s="14" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B38" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C38" s="12">
-        <v>6</v>
-      </c>
-      <c r="D38" s="13" t="s">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B39" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" s="12">
+        <v>6</v>
+      </c>
+      <c r="D39" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E38" s="14" t="s">
+      <c r="E39" s="14" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B39" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C39" s="12">
-        <v>6</v>
-      </c>
-      <c r="D39" s="13" t="s">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B40" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="12">
+        <v>6</v>
+      </c>
+      <c r="D40" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E39" s="14" t="s">
+      <c r="E40" s="14" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B40" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C40" s="12">
-        <v>6</v>
-      </c>
-      <c r="D40" s="13" t="s">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B41" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" s="12">
+        <v>6</v>
+      </c>
+      <c r="D41" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="E40" s="14" t="s">
+      <c r="E41" s="14" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B41" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C41" s="12">
-        <v>6</v>
-      </c>
-      <c r="D41" s="13" t="s">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B42" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="12">
+        <v>6</v>
+      </c>
+      <c r="D42" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E41" s="14" t="s">
+      <c r="E42" s="14" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B42" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C42" s="12">
-        <v>6</v>
-      </c>
-      <c r="D42" s="13" t="s">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B43" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="12">
+        <v>6</v>
+      </c>
+      <c r="D43" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E42" s="14" t="s">
+      <c r="E43" s="14" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B43" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C43" s="12">
-        <v>6</v>
-      </c>
-      <c r="D43" s="13" t="s">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B44" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="12">
+        <v>6</v>
+      </c>
+      <c r="D44" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="E43" s="14" t="s">
+      <c r="E44" s="14" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B44" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C44" s="12">
-        <v>6</v>
-      </c>
-      <c r="D44" s="13" t="s">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B45" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C45" s="12">
+        <v>6</v>
+      </c>
+      <c r="D45" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E44" s="14" t="s">
+      <c r="E45" s="14" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B45" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C45" s="12">
-        <v>6</v>
-      </c>
-      <c r="D45" s="13" t="s">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B46" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C46" s="12">
+        <v>6</v>
+      </c>
+      <c r="D46" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E45" s="14" t="s">
+      <c r="E46" s="14" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B46" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C46" s="12">
-        <v>6</v>
-      </c>
-      <c r="D46" s="13" t="s">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B47" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C47" s="12">
+        <v>6</v>
+      </c>
+      <c r="D47" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="E46" s="14" t="s">
+      <c r="E47" s="14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B47" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C47" s="12">
-        <v>6</v>
-      </c>
-      <c r="D47" s="13" t="s">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B48" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C48" s="12">
+        <v>6</v>
+      </c>
+      <c r="D48" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="E47" s="14" t="s">
+      <c r="E48" s="14" t="s">
         <v>64</v>
-      </c>
-    </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B48" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C48" s="12">
-        <v>6</v>
-      </c>
-      <c r="D48" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="E48" s="14" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.25">
@@ -1705,10 +1712,10 @@
         <v>6</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.25">
@@ -1719,10 +1726,10 @@
         <v>6</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.25">
@@ -1733,10 +1740,10 @@
         <v>6</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.25">
@@ -1747,10 +1754,10 @@
         <v>6</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.25">
@@ -1761,10 +1768,10 @@
         <v>6</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.25">
@@ -1775,10 +1782,10 @@
         <v>6</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.25">
@@ -1789,10 +1796,10 @@
         <v>6</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.25">
@@ -1803,10 +1810,10 @@
         <v>6</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.25">
@@ -1817,10 +1824,10 @@
         <v>6</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E57" s="14" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.25">
@@ -1831,10 +1838,10 @@
         <v>6</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.25">
@@ -1845,46 +1852,46 @@
         <v>6</v>
       </c>
       <c r="D59" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="E59" s="14" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B60" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C60" s="12">
+        <v>6</v>
+      </c>
+      <c r="D60" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="E59" s="14" t="s">
+      <c r="E60" s="14" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="61" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B61" s="23" t="s">
+    <row r="62" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B62" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="C61" s="24"/>
-      <c r="D61" s="24"/>
-      <c r="E61" s="24"/>
-    </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B62" s="1" t="s">
+      <c r="C62" s="24"/>
+      <c r="D62" s="24"/>
+      <c r="E62" s="24"/>
+    </row>
+    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B63" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="D63" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E62" s="2" t="s">
+      <c r="E63" s="2" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B63" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C63" s="12">
-        <v>6</v>
-      </c>
-      <c r="D63" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E63" s="14" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="64" spans="2:5" x14ac:dyDescent="0.25">
@@ -1895,10 +1902,10 @@
         <v>6</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E64" s="14" t="s">
-        <v>34</v>
+        <v>161</v>
       </c>
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.25">
@@ -1909,10 +1916,10 @@
         <v>6</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E65" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.25">
@@ -1923,10 +1930,10 @@
         <v>6</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.25">
@@ -1937,10 +1944,10 @@
         <v>6</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E67" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.25">
@@ -1951,10 +1958,10 @@
         <v>6</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.25">
@@ -1965,10 +1972,10 @@
         <v>6</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.25">
@@ -1979,10 +1986,10 @@
         <v>6</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.25">
@@ -1993,10 +2000,10 @@
         <v>6</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.25">
@@ -2007,46 +2014,46 @@
         <v>6</v>
       </c>
       <c r="D72" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E72" s="14" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="73" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B73" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C73" s="12">
+        <v>6</v>
+      </c>
+      <c r="D73" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E72" s="14" t="s">
+      <c r="E73" s="14" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="75" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B75" s="23" t="s">
+    <row r="76" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B76" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="C75" s="24"/>
-      <c r="D75" s="24"/>
-      <c r="E75" s="24"/>
-    </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B76" s="1" t="s">
+      <c r="C76" s="24"/>
+      <c r="D76" s="24"/>
+      <c r="E76" s="24"/>
+    </row>
+    <row r="77" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B77" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C77" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="D77" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E76" s="2" t="s">
+      <c r="E77" s="2" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B77" s="12">
-        <v>1</v>
-      </c>
-      <c r="C77" s="12">
-        <v>1</v>
-      </c>
-      <c r="D77" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E77" s="14" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="78" spans="2:5" x14ac:dyDescent="0.25">
@@ -2057,10 +2064,10 @@
         <v>1</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E78" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="79" spans="2:5" x14ac:dyDescent="0.25">
@@ -2071,10 +2078,10 @@
         <v>1</v>
       </c>
       <c r="D79" s="13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E79" s="14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="80" spans="2:5" x14ac:dyDescent="0.25">
@@ -2085,118 +2092,118 @@
         <v>1</v>
       </c>
       <c r="D80" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E80" s="14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="81" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B81" s="12">
+        <v>1</v>
+      </c>
+      <c r="C81" s="12">
+        <v>1</v>
+      </c>
+      <c r="D81" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E80" s="14" t="s">
+      <c r="E81" s="14" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="84" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B84" s="5"/>
-      <c r="C84" s="7" t="s">
+    <row r="85" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B85" s="5"/>
+      <c r="C85" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D84" s="5"/>
-      <c r="E84" s="6"/>
-    </row>
-    <row r="86" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B86" s="25" t="s">
+      <c r="D85" s="5"/>
+      <c r="E85" s="6"/>
+    </row>
+    <row r="87" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B87" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="C86" s="24"/>
-      <c r="D86" s="24"/>
-      <c r="E86" s="24"/>
-    </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B87" s="1" t="s">
+      <c r="C87" s="24"/>
+      <c r="D87" s="24"/>
+      <c r="E87" s="24"/>
+    </row>
+    <row r="88" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B88" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D87" s="9" t="s">
+      <c r="D88" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E87" s="2" t="s">
+      <c r="E88" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B88" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C88" s="12">
-        <v>6</v>
-      </c>
-      <c r="D88" s="15" t="s">
+    <row r="89" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B89" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C89" s="12">
+        <v>6</v>
+      </c>
+      <c r="D89" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="E88" s="16" t="s">
+      <c r="E89" s="16" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B89" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C89" s="17">
-        <v>6</v>
-      </c>
-      <c r="D89" s="18" t="s">
+    <row r="90" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B90" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C90" s="17">
+        <v>6</v>
+      </c>
+      <c r="D90" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="E89" s="19" t="s">
+      <c r="E90" s="19" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="91" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B91" s="25" t="s">
+    <row r="92" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B92" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="C91" s="24"/>
-      <c r="D91" s="24"/>
-      <c r="E91" s="24"/>
-    </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B92" s="1" t="s">
+      <c r="C92" s="24"/>
+      <c r="D92" s="24"/>
+      <c r="E92" s="24"/>
+    </row>
+    <row r="93" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B93" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D92" s="9" t="s">
+      <c r="D93" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E92" s="2" t="s">
+      <c r="E93" s="2" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B93" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C93" s="12">
-        <v>6</v>
-      </c>
-      <c r="D93" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="E93" s="16" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="94" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B94" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C94" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D94" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="E94" s="21" t="s">
-        <v>104</v>
+      <c r="C94" s="12">
+        <v>6</v>
+      </c>
+      <c r="D94" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="E94" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="95" spans="2:5" x14ac:dyDescent="0.25">
@@ -2206,8 +2213,8 @@
       <c r="C95" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D95" s="15" t="s">
-        <v>106</v>
+      <c r="D95" s="18" t="s">
+        <v>105</v>
       </c>
       <c r="E95" s="21" t="s">
         <v>104</v>
@@ -2220,8 +2227,8 @@
       <c r="C96" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D96" s="22" t="s">
-        <v>107</v>
+      <c r="D96" s="15" t="s">
+        <v>106</v>
       </c>
       <c r="E96" s="21" t="s">
         <v>104</v>
@@ -2234,8 +2241,8 @@
       <c r="C97" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D97" s="15" t="s">
-        <v>108</v>
+      <c r="D97" s="22" t="s">
+        <v>107</v>
       </c>
       <c r="E97" s="21" t="s">
         <v>104</v>
@@ -2248,8 +2255,8 @@
       <c r="C98" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D98" s="18" t="s">
-        <v>105</v>
+      <c r="D98" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E98" s="21" t="s">
         <v>104</v>
@@ -2262,8 +2269,8 @@
       <c r="C99" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D99" s="15" t="s">
-        <v>109</v>
+      <c r="D99" s="18" t="s">
+        <v>105</v>
       </c>
       <c r="E99" s="21" t="s">
         <v>104</v>
@@ -2276,8 +2283,8 @@
       <c r="C100" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D100" s="18" t="s">
-        <v>110</v>
+      <c r="D100" s="15" t="s">
+        <v>109</v>
       </c>
       <c r="E100" s="21" t="s">
         <v>104</v>
@@ -2290,8 +2297,8 @@
       <c r="C101" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D101" s="15" t="s">
-        <v>111</v>
+      <c r="D101" s="18" t="s">
+        <v>110</v>
       </c>
       <c r="E101" s="21" t="s">
         <v>104</v>
@@ -2304,8 +2311,8 @@
       <c r="C102" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D102" s="22" t="s">
-        <v>112</v>
+      <c r="D102" s="15" t="s">
+        <v>111</v>
       </c>
       <c r="E102" s="21" t="s">
         <v>104</v>
@@ -2318,8 +2325,8 @@
       <c r="C103" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D103" s="15" t="s">
-        <v>113</v>
+      <c r="D103" s="22" t="s">
+        <v>112</v>
       </c>
       <c r="E103" s="21" t="s">
         <v>104</v>
@@ -2332,8 +2339,8 @@
       <c r="C104" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D104" s="22" t="s">
-        <v>114</v>
+      <c r="D104" s="15" t="s">
+        <v>113</v>
       </c>
       <c r="E104" s="21" t="s">
         <v>104</v>
@@ -2346,8 +2353,8 @@
       <c r="C105" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D105" s="15" t="s">
-        <v>115</v>
+      <c r="D105" s="22" t="s">
+        <v>114</v>
       </c>
       <c r="E105" s="21" t="s">
         <v>104</v>
@@ -2360,8 +2367,8 @@
       <c r="C106" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D106" s="18" t="s">
-        <v>116</v>
+      <c r="D106" s="15" t="s">
+        <v>115</v>
       </c>
       <c r="E106" s="21" t="s">
         <v>104</v>
@@ -2374,8 +2381,8 @@
       <c r="C107" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D107" s="15" t="s">
-        <v>117</v>
+      <c r="D107" s="18" t="s">
+        <v>116</v>
       </c>
       <c r="E107" s="21" t="s">
         <v>104</v>
@@ -2388,8 +2395,8 @@
       <c r="C108" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D108" s="18" t="s">
-        <v>118</v>
+      <c r="D108" s="15" t="s">
+        <v>117</v>
       </c>
       <c r="E108" s="21" t="s">
         <v>104</v>
@@ -2402,8 +2409,8 @@
       <c r="C109" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D109" s="15" t="s">
-        <v>119</v>
+      <c r="D109" s="18" t="s">
+        <v>118</v>
       </c>
       <c r="E109" s="21" t="s">
         <v>104</v>
@@ -2416,8 +2423,8 @@
       <c r="C110" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D110" s="18" t="s">
-        <v>120</v>
+      <c r="D110" s="15" t="s">
+        <v>119</v>
       </c>
       <c r="E110" s="21" t="s">
         <v>104</v>
@@ -2430,8 +2437,8 @@
       <c r="C111" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D111" s="15" t="s">
-        <v>121</v>
+      <c r="D111" s="18" t="s">
+        <v>120</v>
       </c>
       <c r="E111" s="21" t="s">
         <v>104</v>
@@ -2444,8 +2451,8 @@
       <c r="C112" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D112" s="18" t="s">
-        <v>122</v>
+      <c r="D112" s="15" t="s">
+        <v>121</v>
       </c>
       <c r="E112" s="21" t="s">
         <v>104</v>
@@ -2458,8 +2465,8 @@
       <c r="C113" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D113" s="15" t="s">
-        <v>123</v>
+      <c r="D113" s="18" t="s">
+        <v>122</v>
       </c>
       <c r="E113" s="21" t="s">
         <v>104</v>
@@ -2472,8 +2479,8 @@
       <c r="C114" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D114" s="18" t="s">
-        <v>124</v>
+      <c r="D114" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="E114" s="21" t="s">
         <v>104</v>
@@ -2486,8 +2493,8 @@
       <c r="C115" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D115" s="15" t="s">
-        <v>125</v>
+      <c r="D115" s="18" t="s">
+        <v>124</v>
       </c>
       <c r="E115" s="21" t="s">
         <v>104</v>
@@ -2500,8 +2507,8 @@
       <c r="C116" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D116" s="18" t="s">
-        <v>126</v>
+      <c r="D116" s="15" t="s">
+        <v>125</v>
       </c>
       <c r="E116" s="21" t="s">
         <v>104</v>
@@ -2514,8 +2521,8 @@
       <c r="C117" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D117" s="15" t="s">
-        <v>127</v>
+      <c r="D117" s="18" t="s">
+        <v>126</v>
       </c>
       <c r="E117" s="21" t="s">
         <v>104</v>
@@ -2528,47 +2535,47 @@
       <c r="C118" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D118" s="18" t="s">
-        <v>128</v>
+      <c r="D118" s="15" t="s">
+        <v>127</v>
       </c>
       <c r="E118" s="21" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="120" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B120" s="25" t="s">
+    <row r="119" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B119" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C119" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="D119" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="E119" s="21" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="121" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B121" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="C120" s="24"/>
-      <c r="D120" s="24"/>
-      <c r="E120" s="24"/>
-    </row>
-    <row r="121" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B121" s="1" t="s">
+      <c r="C121" s="24"/>
+      <c r="D121" s="24"/>
+      <c r="E121" s="24"/>
+    </row>
+    <row r="122" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B122" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D121" s="9" t="s">
+      <c r="D122" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E121" s="2" t="s">
+      <c r="E122" s="2" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="122" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B122" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C122" s="12">
-        <v>2</v>
-      </c>
-      <c r="D122" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="E122" s="16" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="123" spans="2:5" x14ac:dyDescent="0.25">
@@ -2578,8 +2585,8 @@
       <c r="C123" s="12">
         <v>2</v>
       </c>
-      <c r="D123" s="18" t="s">
-        <v>132</v>
+      <c r="D123" s="15" t="s">
+        <v>131</v>
       </c>
       <c r="E123" s="16" t="s">
         <v>130</v>
@@ -2592,8 +2599,8 @@
       <c r="C124" s="12">
         <v>2</v>
       </c>
-      <c r="D124" s="15" t="s">
-        <v>133</v>
+      <c r="D124" s="18" t="s">
+        <v>132</v>
       </c>
       <c r="E124" s="16" t="s">
         <v>130</v>
@@ -2606,8 +2613,8 @@
       <c r="C125" s="12">
         <v>2</v>
       </c>
-      <c r="D125" s="22" t="s">
-        <v>134</v>
+      <c r="D125" s="15" t="s">
+        <v>133</v>
       </c>
       <c r="E125" s="16" t="s">
         <v>130</v>
@@ -2620,8 +2627,8 @@
       <c r="C126" s="12">
         <v>2</v>
       </c>
-      <c r="D126" s="15" t="s">
-        <v>135</v>
+      <c r="D126" s="22" t="s">
+        <v>134</v>
       </c>
       <c r="E126" s="16" t="s">
         <v>130</v>
@@ -2634,8 +2641,8 @@
       <c r="C127" s="12">
         <v>2</v>
       </c>
-      <c r="D127" s="18" t="s">
-        <v>136</v>
+      <c r="D127" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="E127" s="16" t="s">
         <v>130</v>
@@ -2648,8 +2655,8 @@
       <c r="C128" s="12">
         <v>2</v>
       </c>
-      <c r="D128" s="15" t="s">
-        <v>137</v>
+      <c r="D128" s="18" t="s">
+        <v>136</v>
       </c>
       <c r="E128" s="16" t="s">
         <v>130</v>
@@ -2662,8 +2669,8 @@
       <c r="C129" s="12">
         <v>2</v>
       </c>
-      <c r="D129" s="22" t="s">
-        <v>138</v>
+      <c r="D129" s="15" t="s">
+        <v>137</v>
       </c>
       <c r="E129" s="16" t="s">
         <v>130</v>
@@ -2676,8 +2683,8 @@
       <c r="C130" s="12">
         <v>2</v>
       </c>
-      <c r="D130" s="15" t="s">
-        <v>139</v>
+      <c r="D130" s="22" t="s">
+        <v>138</v>
       </c>
       <c r="E130" s="16" t="s">
         <v>130</v>
@@ -2690,8 +2697,8 @@
       <c r="C131" s="12">
         <v>2</v>
       </c>
-      <c r="D131" s="22" t="s">
-        <v>140</v>
+      <c r="D131" s="15" t="s">
+        <v>139</v>
       </c>
       <c r="E131" s="16" t="s">
         <v>130</v>
@@ -2704,8 +2711,8 @@
       <c r="C132" s="12">
         <v>2</v>
       </c>
-      <c r="D132" s="15" t="s">
-        <v>141</v>
+      <c r="D132" s="22" t="s">
+        <v>140</v>
       </c>
       <c r="E132" s="16" t="s">
         <v>130</v>
@@ -2718,8 +2725,8 @@
       <c r="C133" s="12">
         <v>2</v>
       </c>
-      <c r="D133" s="22" t="s">
-        <v>142</v>
+      <c r="D133" s="15" t="s">
+        <v>141</v>
       </c>
       <c r="E133" s="16" t="s">
         <v>130</v>
@@ -2732,8 +2739,8 @@
       <c r="C134" s="12">
         <v>2</v>
       </c>
-      <c r="D134" s="15" t="s">
-        <v>143</v>
+      <c r="D134" s="22" t="s">
+        <v>142</v>
       </c>
       <c r="E134" s="16" t="s">
         <v>130</v>
@@ -2746,8 +2753,8 @@
       <c r="C135" s="12">
         <v>2</v>
       </c>
-      <c r="D135" s="18" t="s">
-        <v>144</v>
+      <c r="D135" s="15" t="s">
+        <v>143</v>
       </c>
       <c r="E135" s="16" t="s">
         <v>130</v>
@@ -2760,8 +2767,8 @@
       <c r="C136" s="12">
         <v>2</v>
       </c>
-      <c r="D136" s="15" t="s">
-        <v>145</v>
+      <c r="D136" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="E136" s="16" t="s">
         <v>130</v>
@@ -2774,8 +2781,8 @@
       <c r="C137" s="12">
         <v>2</v>
       </c>
-      <c r="D137" s="18" t="s">
-        <v>146</v>
+      <c r="D137" s="15" t="s">
+        <v>145</v>
       </c>
       <c r="E137" s="16" t="s">
         <v>130</v>
@@ -2788,8 +2795,8 @@
       <c r="C138" s="12">
         <v>2</v>
       </c>
-      <c r="D138" s="15" t="s">
-        <v>147</v>
+      <c r="D138" s="18" t="s">
+        <v>146</v>
       </c>
       <c r="E138" s="16" t="s">
         <v>130</v>
@@ -2802,8 +2809,8 @@
       <c r="C139" s="12">
         <v>2</v>
       </c>
-      <c r="D139" s="18" t="s">
-        <v>148</v>
+      <c r="D139" s="15" t="s">
+        <v>147</v>
       </c>
       <c r="E139" s="16" t="s">
         <v>130</v>
@@ -2816,8 +2823,8 @@
       <c r="C140" s="12">
         <v>2</v>
       </c>
-      <c r="D140" s="15" t="s">
-        <v>149</v>
+      <c r="D140" s="18" t="s">
+        <v>148</v>
       </c>
       <c r="E140" s="16" t="s">
         <v>130</v>
@@ -2828,10 +2835,10 @@
         <v>5</v>
       </c>
       <c r="C141" s="12">
-        <v>6</v>
-      </c>
-      <c r="D141" s="22" t="s">
-        <v>150</v>
+        <v>2</v>
+      </c>
+      <c r="D141" s="15" t="s">
+        <v>149</v>
       </c>
       <c r="E141" s="16" t="s">
         <v>130</v>
@@ -2842,10 +2849,10 @@
         <v>5</v>
       </c>
       <c r="C142" s="12">
-        <v>2</v>
-      </c>
-      <c r="D142" s="15" t="s">
-        <v>151</v>
+        <v>6</v>
+      </c>
+      <c r="D142" s="22" t="s">
+        <v>150</v>
       </c>
       <c r="E142" s="16" t="s">
         <v>130</v>
@@ -2858,8 +2865,8 @@
       <c r="C143" s="12">
         <v>2</v>
       </c>
-      <c r="D143" s="18" t="s">
-        <v>152</v>
+      <c r="D143" s="15" t="s">
+        <v>151</v>
       </c>
       <c r="E143" s="16" t="s">
         <v>130</v>
@@ -2870,10 +2877,10 @@
         <v>5</v>
       </c>
       <c r="C144" s="12">
-        <v>6</v>
-      </c>
-      <c r="D144" s="15" t="s">
-        <v>153</v>
+        <v>2</v>
+      </c>
+      <c r="D144" s="18" t="s">
+        <v>152</v>
       </c>
       <c r="E144" s="16" t="s">
         <v>130</v>
@@ -2886,8 +2893,8 @@
       <c r="C145" s="12">
         <v>6</v>
       </c>
-      <c r="D145" s="18" t="s">
-        <v>154</v>
+      <c r="D145" s="15" t="s">
+        <v>153</v>
       </c>
       <c r="E145" s="16" t="s">
         <v>130</v>
@@ -2900,8 +2907,8 @@
       <c r="C146" s="12">
         <v>6</v>
       </c>
-      <c r="D146" s="15" t="s">
-        <v>155</v>
+      <c r="D146" s="18" t="s">
+        <v>154</v>
       </c>
       <c r="E146" s="16" t="s">
         <v>130</v>
@@ -2914,8 +2921,8 @@
       <c r="C147" s="12">
         <v>6</v>
       </c>
-      <c r="D147" s="22" t="s">
-        <v>156</v>
+      <c r="D147" s="15" t="s">
+        <v>155</v>
       </c>
       <c r="E147" s="16" t="s">
         <v>130</v>
@@ -2926,29 +2933,43 @@
         <v>5</v>
       </c>
       <c r="C148" s="12">
-        <v>2</v>
-      </c>
-      <c r="D148" s="15" t="s">
-        <v>157</v>
+        <v>6</v>
+      </c>
+      <c r="D148" s="22" t="s">
+        <v>156</v>
       </c>
       <c r="E148" s="16" t="s">
         <v>130</v>
       </c>
     </row>
+    <row r="149" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B149" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C149" s="12">
+        <v>2</v>
+      </c>
+      <c r="D149" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="E149" s="16" t="s">
+        <v>130</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B63:E72">
-    <sortCondition ref="D63:D72"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B64:E73">
+    <sortCondition ref="D64:D73"/>
   </sortState>
   <mergeCells count="9">
-    <mergeCell ref="B75:E75"/>
-    <mergeCell ref="B86:E86"/>
-    <mergeCell ref="B91:E91"/>
-    <mergeCell ref="B120:E120"/>
+    <mergeCell ref="B76:E76"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B92:E92"/>
+    <mergeCell ref="B121:E121"/>
     <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B35:E35"/>
     <mergeCell ref="B15:E15"/>
     <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="B62:E62"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
